--- a/informed_consent_forms/012_nontraditional_learning_experience_recording_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/012_nontraditional_learning_experience_recording_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>record_video</t>
+          <t>record video</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>record_phone</t>
+          <t>record phone</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>record_computer</t>
+          <t>record computer</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>record_other</t>
+          <t>record other</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>record_audio_phone</t>
+          <t>record audio phone</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>record_interview</t>
+          <t>record interview</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>record_meeting</t>
+          <t>record meeting</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>record_other_device</t>
+          <t>record other device</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>record_consent</t>
+          <t>record consent</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>record_signature</t>
+          <t>record signature</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>record_note_taking</t>
+          <t>record note taking</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>record_audio_notes</t>
+          <t>record audio notes</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>record_other_notes</t>
+          <t>record other notes</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>participant_permission_given</t>
+          <t>participant permission given</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>participant_permission_not_given</t>
+          <t>participant permission not given</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>participant_permission_revoke</t>
+          <t>participant permission revoke</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>participant_permission_not_revoke</t>
+          <t>participant permission not revoke</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>participant_permission_change</t>
+          <t>participant permission change</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>participant_permission_not_change</t>
+          <t>participant permission not change</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>participant_permission_end_date</t>
+          <t>participant permission end date</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>participant_permission_no_date</t>
+          <t>participant permission no date</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>participant_permission_reason</t>
+          <t>participant permission reason</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>participant_permission_no_reason</t>
+          <t>participant permission no reason</t>
         </is>
       </c>
     </row>
